--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_21-12-2025.xlsx
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/12-boards-x-200mm-celotex-xr4200-pir-insulation-2400mm-x-1200mm?_pos=2&amp;_psq=xr4200&amp;_ss=e&amp;_v=1.0</t>
+          <t>£852.50 Pre Sale Price-£889.80</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://insulation4less.co.uk/products/celotex-pl4000-37-5mm</t>
+          <t>£26.89</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPConnectionPool(host='www.farmtotablecoop.com', port=80): Max retries exceeded with url: /localbuyersguide.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPConnection object at 0x00000155BC0B9690&gt;, 'Connection to www.farmtotablecoop.com timed out. (connect timeout=30)'))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£43.40</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>£41.25</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: 502 Server Error: Bad Gateway for url: http://www.farmtotablecoop.com/localbuyersguide.html</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
